--- a/src/main/resources/xlsx/user.xlsx
+++ b/src/main/resources/xlsx/user.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\backend\template-code\src\main\resources\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBB75870-4F73-4626-9E99-0D0505ECD065}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE67BF2D-FCE6-4564-8DEB-0A7924B4E5C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -88,14 +88,6 @@
     <t>测试用户2</t>
   </si>
   <si>
-    <t>日期时间</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>日期</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>角色</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -105,6 +97,14 @@
   </si>
   <si>
     <t>普通用户</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>创建时间</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>更新时间</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -565,13 +565,13 @@
         <v>7</v>
       </c>
       <c r="I1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K1" s="3" t="s">
         <v>22</v>
-      </c>
-      <c r="J1" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="K1" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.4">
@@ -606,7 +606,7 @@
         <v>46186</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="14.4">
@@ -641,7 +641,7 @@
         <v>46186</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
